--- a/Data/RimMarket - 3817820660/RimMarket - 3817820660.xlsx
+++ b/Data/RimMarket - 3817820660/RimMarket - 3817820660.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">a tackle</t>
   </si>
   <si>
-    <t xml:space="preserve">몸싸움</t>
+    <t xml:space="preserve">태클</t>
   </si>
   <si>
     <t xml:space="preserve">HediffDef+RimMarket_Subdued.description</t>
@@ -115,7 +115,7 @@
     <t xml:space="preserve">held a stall at their market</t>
   </si>
   <si>
-    <t xml:space="preserve">자신들의 시장에서 노점을 운영함</t>
+    <t xml:space="preserve">상대 세력의 시장에서 노점을 운영함</t>
   </si>
   <si>
     <t xml:space="preserve">HistoryEventDef+RimMarket_FairPrize.label</t>
@@ -753,7 +753,7 @@
     <t xml:space="preserve">They sold people at our market today. I looked the other way. It did not help much.</t>
   </si>
   <si>
-    <t xml:space="preserve">오늘 우리 시장에서 사람들을 팔았다. 고개를 돌려 외면했다. 별 도움이 되지는 않았다.</t>
+    <t xml:space="preserve">오늘 우리 시장에서 사람들이 팔려 나갔다. 고개를 돌려 외면했다. 별 도움이 되지는 않았다.</t>
   </si>
   <si>
     <t xml:space="preserve">ThoughtDef+RimMarket_SlaveAuctionHeld.stages.2.label</t>
@@ -1059,7 +1059,7 @@
     <t xml:space="preserve">The arrival fee never goes above this, in silver.</t>
   </si>
   <si>
-    <t xml:space="preserve">도착 시 사용료는 이 은 금액을 넘지 않습니다.</t>
+    <t xml:space="preserve">도착 시 사용료는 이 금액을 넘지 않습니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.Settings.SharePercentHint</t>
@@ -1383,7 +1383,7 @@
     <t xml:space="preserve">Market inn, silver per night</t>
   </si>
   <si>
-    <t xml:space="preserve">시장 여관의 1박당 은 요금</t>
+    <t xml:space="preserve">시장 여관의 1박당 요금</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.Settings.InnPriceHint</t>
@@ -1395,7 +1395,7 @@
     <t xml:space="preserve">What each lodger pays for a night in a bed set to Market inn. The merchant pays for the caravan's guards, shoppers pay for themselves. A miserable room at a stiff price is remembered. Zero keeps the inn free.</t>
   </si>
   <si>
-    <t xml:space="preserve">시장 여관으로 지정한 침대에서 하룻밤을 보내는 투숙객 한 명당 요금입니다. 상인은 상단 경비원들의 요금을 내고, 쇼핑객은 자신의 요금을 냅니다. 형편없는 방에 비싼 요금을 매기면 잊지 않을 것입니다. 0으로 설정하면 무료로 운영합니다.</t>
+    <t xml:space="preserve">시장 여관으로 지정한 침대에서 하룻밤을 보내는 투숙객 한 명당 요금입니다. 상인은 상단 경비원들의 요금을 내고, 쇼핑객은 자신의 요금을 냅니다. 형편없는 방에 비싼 요금을 매기면 손님들이 기억해 둡니다. 0으로 설정하면 무료로 운영합니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.CommandInnBed</t>
@@ -1683,7 +1683,7 @@
     <t xml:space="preserve">A good reputation brings extra caravans, rarer merchants and better prices. A bad one makes caravans camp outside and prices climb. With this off, the reputation is still kept but changes nothing.</t>
   </si>
   <si>
-    <t xml:space="preserve">평판이 좋으면 상단이 더 많이 찾아오고, 드문 종류의 상인과 더 좋은 가격을 만날 수 있습니다. 평판이 나쁘면 상단은 바깥에서 야영하고 가격도 올라갑니다. 끄면 평판은 계속 기록되지만 아무 영향도 주지 않습니다.</t>
+    <t xml:space="preserve">평판이 좋으면 상단이 더 많이 찾아오고, 드문 종류의 상인도 방문하며 거래 가격도 유리해집니다. 평판이 나쁘면 상단은 바깥에서 야영하고 가격도 올라갑니다. 끄면 평판은 계속 기록되지만 아무 영향도 주지 않습니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.Settings.Thieves</t>
@@ -1887,7 +1887,7 @@
     <t xml:space="preserve">How merchants pay for a stall in this market. Fee on arrival: silver counted on the counter before they set up. No fee: the stall is free. Or follow the mod setting.</t>
   </si>
   <si>
-    <t xml:space="preserve">이 시장에서 상인이 노점 사용료를 내는 방식입니다. 도착 시 사용료: 노점을 열기 전에 계산대에서 은을 셉니다. 사용료 없음: 무료로 이용합니다. 모드 설정을 따를 수도 있습니다.</t>
+    <t xml:space="preserve">이 시장에서 상인이 노점 사용료를 내는 방식입니다. 도착 시 사용료: 노점을 열기 전에 계산대에서 은으로 지불합니다. 사용료 없음: 무료로 이용합니다. 모드 설정을 따를 수도 있습니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.FeeModeDescShare</t>
@@ -1911,7 +1911,7 @@
     <t xml:space="preserve">Close market now</t>
   </si>
   <si>
-    <t xml:space="preserve">시장 즉시 철수</t>
+    <t xml:space="preserve">상인 즉시 철수</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.CloseMarketDesc</t>
@@ -2007,7 +2007,7 @@
     <t xml:space="preserve">The square is not enclosed within {0} cells of the marker. Close it off or set the radius by hand.</t>
   </si>
   <si>
-    <t xml:space="preserve">표식에서 {0}칸 안에 광장을 둘러싸는 경계가 없습니다. 경계를 닫거나 반경을 직접 설정하세요.</t>
+    <t xml:space="preserve">표식에서 {0}칸 이내에 광장이 완전히 둘러싸여 있지 않습니다. 벽이나 울타리로 둘러싸거나 반경을 직접 설정하세요.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.QuarterAutoFit</t>
@@ -2736,7 +2736,7 @@
     <t xml:space="preserve">Change of guard: {0} is coming to take over from {1}</t>
   </si>
   <si>
-    <t xml:space="preserve">경비 교대: {0}(이)가 {1}의 근무를 교대하러 오는 중</t>
+    <t xml:space="preserve">경비 교대: {0}(이)가 {1} 대신 근무하러 오는 중</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.StallGuestSales</t>
@@ -3252,7 +3252,7 @@
     <t xml:space="preserve">The market is full: the {0} caravan waits outside until a merchant leaves.</t>
   </si>
   <si>
-    <t xml:space="preserve">시장의 수용 인원이 가득 찼습니다. {0} 상단은 상인 하나가 떠날 때까지 밖에서 기다립니다.</t>
+    <t xml:space="preserve">시장에서 받을 수 있는 상인 수가 한도에 도달했습니다. {0} 상단은 상인 한 명이 떠날 때까지 밖에서 기다립니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.MessageNoFreeStall</t>
@@ -3348,7 +3348,7 @@
     <t xml:space="preserve">The market is closing: the {0} merchant packs up.</t>
   </si>
   <si>
-    <t xml:space="preserve">시장이 철수합니다. {0} 상인이 짐을 챙깁니다.</t>
+    <t xml:space="preserve">시장 영업을 마칩니다. {0} 상인이 짐을 챙깁니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.MessageStallGone</t>
@@ -3408,7 +3408,7 @@
     <t xml:space="preserve">Market closed: {0} merchant(s) sent packing.</t>
   </si>
   <si>
-    <t xml:space="preserve">시장이 철수했습니다. 상인 {0}명을 돌려보냈습니다.</t>
+    <t xml:space="preserve">시장 상인 {0}명을 돌려보냈습니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.MessageHaggleWon</t>
@@ -4602,7 +4602,7 @@
     <t xml:space="preserve">Current bid: {0} silver by {1}. The gavel falls in {2}.</t>
   </si>
   <si>
-    <t xml:space="preserve">현재 입찰가: {1}의 {0} 은. {2} 후 낙찰됩니다.</t>
+    <t xml:space="preserve">현재 입찰가: {0} 은, 입찰자 {1}. {2} 후 낙찰됩니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.AuctionColonySilver</t>
@@ -4662,7 +4662,7 @@
     <t xml:space="preserve">Bid {1} silver for {0}. If nobody outbids you before the gavel falls, the silver comes out of your stockpiles and {0} is yours, as if bought from the slaver.</t>
   </si>
   <si>
-    <t xml:space="preserve">{0}에게 {1} 은을 입찰합니다. 낙찰될 때까지 더 높은 입찰이 없으면 보관 구역에서 은을 지불하고, 노예 상인에게 직접 구매한 것처럼 {0}(을)를 얻습니다.</t>
+    <t xml:space="preserve">{0}(을)를 사기 위해 {1} 은을 입찰합니다. 낙찰될 때까지 더 높은 입찰이 없으면 보관 구역에서 은을 지불하고, 노예 상인에게 직접 구매한 것처럼 {0}(을)를 얻습니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.AuctionYouLead</t>
@@ -4686,7 +4686,7 @@
     <t xml:space="preserve">not enough silver in your stockpiles for a bid of {0}</t>
   </si>
   <si>
-    <t xml:space="preserve">보관 구역의 은이 {0} 입찰에 부족함</t>
+    <t xml:space="preserve">보관 구역에 {0} 입찰에 필요한 은이 부족함</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.AuctionAnnounced</t>
@@ -4794,7 +4794,7 @@
     <t xml:space="preserve">No takers for {0}. The slaver keeps them.</t>
   </si>
   <si>
-    <t xml:space="preserve">{0}에게 입찰한 사람이 없습니다. 노예 상인이 그대로 데리고 있습니다.</t>
+    <t xml:space="preserve">{0}(을)를 사겠다는 사람이 없습니다. 노예 상인이 그대로 데리고 있습니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.AuctionNoSlaves</t>
@@ -4938,7 +4938,7 @@
     <t xml:space="preserve">the merchant getting hurt</t>
   </si>
   <si>
-    <t xml:space="preserve">상인이 다침</t>
+    <t xml:space="preserve">상인의 부상</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.ReasonCaravanHurt</t>
@@ -4950,7 +4950,7 @@
     <t xml:space="preserve">losing people from the caravan</t>
   </si>
   <si>
-    <t xml:space="preserve">상단 인원을 잃음</t>
+    <t xml:space="preserve">상단 인원의 손실</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.ReasonSafe</t>
@@ -4974,7 +4974,7 @@
     <t xml:space="preserve">a full market day</t>
   </si>
   <si>
-    <t xml:space="preserve">하루를 온전히 장사함</t>
+    <t xml:space="preserve">하루 내내 이어진 장사</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.ReasonClosedEarly</t>
@@ -4986,7 +4986,7 @@
     <t xml:space="preserve">being sent packing early</t>
   </si>
   <si>
-    <t xml:space="preserve">일찍 철수를 요구받음</t>
+    <t xml:space="preserve">이른 철수 요구</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.ReasonStallGone</t>
@@ -4998,7 +4998,7 @@
     <t xml:space="preserve">losing the stall</t>
   </si>
   <si>
-    <t xml:space="preserve">노점을 잃음</t>
+    <t xml:space="preserve">노점의 상실</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.ReasonNoFee</t>
@@ -5058,7 +5058,7 @@
     <t xml:space="preserve">being taxed twice in one day</t>
   </si>
   <si>
-    <t xml:space="preserve">하루에 두 번 세금을 냄</t>
+    <t xml:space="preserve">하루에 두 번 낸 세금</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.ReasonHandsome</t>
@@ -5106,7 +5106,7 @@
     <t xml:space="preserve">good sales to your guests</t>
   </si>
   <si>
-    <t xml:space="preserve">당신의 손님에게 잘 팔림</t>
+    <t xml:space="preserve">손님에게서 올린 높은 매출</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.ReasonBusy</t>
@@ -5118,7 +5118,7 @@
     <t xml:space="preserve">plenty of browsers</t>
   </si>
   <si>
-    <t xml:space="preserve">구경하는 사람이 많음</t>
+    <t xml:space="preserve">많은 구경꾼</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.ReasonInnFine</t>
@@ -5130,7 +5130,7 @@
     <t xml:space="preserve">a good night at your inn</t>
   </si>
   <si>
-    <t xml:space="preserve">여관에서 편안한 밤을 보냄</t>
+    <t xml:space="preserve">여관에서 보낸 편안한 밤</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.ReasonInnPoor</t>
@@ -5142,7 +5142,7 @@
     <t xml:space="preserve">a flea-bitten night at your inn</t>
   </si>
   <si>
-    <t xml:space="preserve">여관에서 벼룩에 시달림</t>
+    <t xml:space="preserve">여관에서 보낸 불편한 밤</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.ReasonInnSteep</t>
@@ -5154,7 +5154,7 @@
     <t xml:space="preserve">paying through the nose for a bed</t>
   </si>
   <si>
-    <t xml:space="preserve">침대 하나에 바가지를 씀</t>
+    <t xml:space="preserve">터무니없이 비싼 침대 요금</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.ReasonThiefCaught</t>
@@ -5166,7 +5166,7 @@
     <t xml:space="preserve">a thief caught</t>
   </si>
   <si>
-    <t xml:space="preserve">도둑을 잡음</t>
+    <t xml:space="preserve">도둑 체포</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.ReasonThiefDeterred</t>
@@ -5178,7 +5178,7 @@
     <t xml:space="preserve">a thief scared off</t>
   </si>
   <si>
-    <t xml:space="preserve">도둑을 쫓아냄</t>
+    <t xml:space="preserve">도둑 접근 저지</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.ReasonRobbed</t>
@@ -5190,7 +5190,7 @@
     <t xml:space="preserve">a thief who got away</t>
   </si>
   <si>
-    <t xml:space="preserve">도둑이 달아남</t>
+    <t xml:space="preserve">도둑의 도주</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.ReasonHaggledHard</t>
@@ -5262,7 +5262,7 @@
     <t xml:space="preserve">100%: shoppers come twice as often to a stall selling at 85% of value or less, and about a third as often at double the value. 0%: prices change nothing about how often they come, only whether they buy. 200%: bargains are the talk of the region.</t>
   </si>
   <si>
-    <t xml:space="preserve">100%: 상품 가치의 85% 이하에 판매하는 노점에는 쇼핑객이 두 배 자주 찾아오며, 두 배 가격에 판매하는 노점에는 약 3분의 1 빈도로 찾아옵니다. 0%: 가격은 구매 여부에만 영향을 주며 방문 빈도를 바꾸지 않습니다. 200%: 저렴한 상품이 지역 전체의 화젯거리가 됩니다.</t>
+    <t xml:space="preserve">100%: 상품 가치의 85% 이하에 판매하는 노점에는 쇼핑객이 두 배의 빈도로 찾아오며, 상품 가치의 두 배 가격에 판매하는 노점에는 약 3분의 1의 빈도로 찾아옵니다. 0%: 가격은 구매 여부에만 영향을 주며 방문 빈도를 바꾸지 않습니다. 200%: 저렴한 상품이 지역 전체의 화젯거리가 됩니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.Settings.Shopkeepers</t>
@@ -5286,7 +5286,7 @@
     <t xml:space="preserve">Off: colony stalls sell on their own, on trust. On: a colonist with the Shopkeep work type has to stand at the counter while customers are in town. Their Social skill raises prices, customers buy a little more readily, and every sale teaches them something. The Shopkeep column appears in the Work tab after a restart.</t>
   </si>
   <si>
-    <t xml:space="preserve">끄면 정착지 노점이 신뢰에 맡겨 자동으로 판매합니다. 켜면 고객이 마을에 있는 동안 점포 관리 작업을 맡은 정착민이 계산대를 지켜야 합니다. 사교 능력이 높으면 판매 가격이 올라가고, 고객은 조금 더 쉽게 구매하며, 판매할 때마다 담당자가 경험을 얻습니다. 작업 탭의 점포 관리 항목은 게임을 재시작하면 나타납니다.</t>
+    <t xml:space="preserve">끄면 손님의 양심에 맡겨 정착지 노점을 무인으로 운영합니다. 켜면 고객이 마을에 있는 동안 점포 관리 작업을 맡은 정착민이 계산대를 지켜야 합니다. 사교 능력이 높으면 판매 가격이 올라가고, 고객은 조금 더 쉽게 구매하며, 판매할 때마다 담당자가 경험을 얻습니다. 작업 탭의 점포 관리 항목은 게임을 재시작하면 나타납니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.FairAnnounceLabel</t>
@@ -5646,7 +5646,7 @@
     <t xml:space="preserve">The Great Fair runs until {0}h. Expect caravans, crowds, cheerful colonists and busy pickpockets.</t>
   </si>
   <si>
-    <t xml:space="preserve">대장터는 {0}시까지 열립니다. 상단과 인파, 즐거워하는 정착민, 바쁜 소매치기들이 찾아올 것입니다.</t>
+    <t xml:space="preserve">대장터는 {0}시까지 열립니다. 상단과 인파가 몰려오고, 정착민은 즐거워하며 소매치기는 바빠질 것입니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.Settings.Fair</t>
@@ -5718,7 +5718,7 @@
     <t xml:space="preserve">Adds a Trade routes option when you talk to a faction by comms console, or by bird post with Medieval Overhaul. For a fee in silver, one of their towns sends a convoy to your market every week or two, and you can watch it travel on the world map. Roads near hostile towns (or through hostile territory, with Faction Territories and Vassalage) get convoys ambushed; an escort costs more and helps. Off: no new routes and no convoys leave, but existing routes are kept.</t>
   </si>
   <si>
-    <t xml:space="preserve">통신기로 세력과 대화할 때 무역로 항목을 추가합니다. Medieval Overhaul이 있으면 새 우편으로도 이용할 수 있습니다. 은을 지불하면 해당 세력의 마을에서 1~2주마다 시장으로 수송대를 보내며, 세계 지도에서 이동을 지켜볼 수 있습니다. 적대적인 마을 근처를 지나거나, Faction Territories and Vassalage가 있을 때 적대 영토를 지나는 수송대는 매복 공격을 받을 수 있습니다. 호위를 붙이면 비용이 더 들지만 도움이 됩니다. 끄면 새 무역로를 열 수 없고 수송대도 출발하지 않지만, 기존 무역로는 유지됩니다.</t>
+    <t xml:space="preserve">통신기로 세력과 대화할 때 무역로 항목을 추가합니다. Medieval Overhaul이 있으면 전서구로도 이용할 수 있습니다. 은을 지불하면 해당 세력의 마을에서 1~2주마다 시장으로 수송대를 보내며, 세계 지도에서 이동을 지켜볼 수 있습니다. 적대적인 마을 근처를 지나거나, Faction Territories and Vassalage가 있을 때 적대 영토를 지나는 수송대는 매복 공격을 받을 수 있습니다. 호위를 붙이면 비용이 더 들지만 도움이 됩니다. 끄면 새 무역로를 열 수 없고 수송대도 출발하지 않지만, 기존 무역로는 유지됩니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.Settings.RouteOpenCost</t>
@@ -6029,7 +6029,7 @@
     <t xml:space="preserve">{0} can no longer fill your order from {1}. {2} silver comes back.</t>
   </si>
   <si>
-    <t xml:space="preserve">{0}(이)가 더 이상 {1}의 주문을 이행할 수 없습니다. {2} 은이 반환됩니다.</t>
+    <t xml:space="preserve">{0}(이)가 더 이상 {1}에서 주문 상품을 보내 줄 수 없습니다. {2} 은이 반환됩니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.OrderCancelledHostile</t>
@@ -6041,7 +6041,7 @@
     <t xml:space="preserve">{0} turned on you, and your order from {1} with it. {2} silver comes back, which is more than most enemies would do.</t>
   </si>
   <si>
-    <t xml:space="preserve">{0}(이)가 적대적으로 돌아섰으며, {1}의 주문도 취소되었습니다. {2} 은이 반환됩니다. 적이 돈까지 돌려주는 일은 드뭅니다.</t>
+    <t xml:space="preserve">{0}(이)가 적대적으로 돌아서 {1}에서 보내기로 한 주문도 취소되었습니다. {2} 은이 반환됩니다. 적이 돈까지 돌려주는 일은 드뭅니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.OrderCancelledHome</t>
@@ -6053,7 +6053,7 @@
     <t xml:space="preserve">Your order from {1} has nowhere to go. {2} silver comes back.</t>
   </si>
   <si>
-    <t xml:space="preserve">{1}의 주문을 배달할 곳이 없습니다. {2} 은이 반환됩니다.</t>
+    <t xml:space="preserve">{1}에서 보낼 주문 상품을 배달할 곳이 없습니다. {2} 은이 반환됩니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.OrderCancelledNoRoad</t>
@@ -6077,7 +6077,7 @@
     <t xml:space="preserve">Your order from {1} never made it. {2} silver comes back, the rest is somebody else's loot now.</t>
   </si>
   <si>
-    <t xml:space="preserve">{1}의 주문이 끝내 도착하지 못했습니다. {2} 은이 반환됩니다. 나머지는 이제 누군가의 약탈품이 되었습니다.</t>
+    <t xml:space="preserve">{1}에서 보낸 주문 상품이 끝내 도착하지 못했습니다. {2} 은이 반환됩니다. 나머지는 이제 누군가의 약탈품이 되었습니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.OrderWindowValue</t>
@@ -6245,7 +6245,7 @@
     <t xml:space="preserve">Your wanted notice has run its course.</t>
   </si>
   <si>
-    <t xml:space="preserve">구매 공고의 접수가 끝났습니다.</t>
+    <t xml:space="preserve">구매 공고가 종료되었습니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.WantedGizmo</t>
@@ -6419,7 +6419,7 @@
     <t xml:space="preserve">{0}, your best talker, haggles over this offer. One try per offer. Ask for a little and they may say no, ask for too much and they may take the offer back.</t>
   </si>
   <si>
-    <t xml:space="preserve">말솜씨가 가장 좋은 {0}(이)가 이 제안을 흥정합니다. 제안마다 한 번 시도할 수 있습니다. 적게 깎아 달라고 해도 거절할 수 있으며, 너무 많이 요구하면 제안을 철회할 수 있습니다.</t>
+    <t xml:space="preserve">말솜씨가 가장 좋은 {0}(이)가 이 제안에 대해 흥정합니다. 제안마다 한 번 시도할 수 있습니다. 적게 깎아 달라고 해도 거절할 수 있으며, 너무 많이 요구하면 제안을 철회할 수 있습니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.WantedHaggleMenu</t>
@@ -6479,7 +6479,7 @@
     <t xml:space="preserve">Already haggled over this offer.</t>
   </si>
   <si>
-    <t xml:space="preserve">이미 이 제안을 흥정했습니다.</t>
+    <t xml:space="preserve">이미 이 제안에 대해 흥정했습니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.WantedHaggleNoOne</t>
@@ -6839,7 +6839,7 @@
     <t xml:space="preserve">Which town of {0} should send the convoys? The farther it is, the longer the road and the higher the fee.</t>
   </si>
   <si>
-    <t xml:space="preserve">{0}의 어느 마을에서 수송대를 보내게 할까요? 멀수록 길도 길어지고 비용도 높아집니다.</t>
+    <t xml:space="preserve">{0}의 어느 마을에서 수송대를 보내게 할까요? 멀수록 이동 거리와 비용이 늘어납니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.RouteSettlementOption</t>
@@ -6995,7 +6995,7 @@
     <t xml:space="preserve">The trade convoy from {0} was overrun by {1}. The next one leaves as planned.</t>
   </si>
   <si>
-    <t xml:space="preserve">{0}의 무역 수송대가 {1}에게 전멸했습니다. 다음 수송대는 예정대로 출발합니다.</t>
+    <t xml:space="preserve">{0}의 무역 수송대가 {1}의 공격에 무너졌습니다. 다음 수송대는 예정대로 출발합니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.ConvoyUnderAttack</t>
@@ -7223,7 +7223,7 @@
     <t xml:space="preserve">{0} have never traded at your market or hosted your stall. Trade with them there first, then come back.</t>
   </si>
   <si>
-    <t xml:space="preserve">{0}(은)는 아직 당신의 시장에서 거래하거나 당신의 노점을 받아 준 적이 없습니다. 먼저 해당 시장에서 거래한 뒤 돌아오세요.</t>
+    <t xml:space="preserve">{0}(은)는 아직 당신의 시장에서 거래하거나 자기 시장에 당신의 노점을 받아 준 적이 없습니다. 먼저 당신의 시장에서 이 세력과 거래하거나, 이 세력의 시장에서 노점을 운영한 뒤 다시 연락하세요.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.RouteUnknown</t>
@@ -7331,7 +7331,7 @@
     <t xml:space="preserve">The trade route with {0} is closed: {1} is no longer theirs to send convoys from.</t>
   </si>
   <si>
-    <t xml:space="preserve">{0}(와)과의 무역로가 폐쇄되었습니다. 더 이상 {1}(을)를 소유하지 않아 그곳에서 수송대를 보낼 수 없습니다.</t>
+    <t xml:space="preserve">{0}(와)과의 무역로가 폐쇄되었습니다. 해당 세력이 더 이상 {1}(을)를 소유하지 않아 그곳에서 수송대를 보낼 수 없습니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.RouteClosedHostile</t>
@@ -7685,7 +7685,7 @@
     <t xml:space="preserve">Everything starts with the market marker (Architect, Misc). Put it in the middle of your square: every stall within its radius belongs to the market.\n\nSelect it to fit the radius to your walls in one click, set the stall fee, open or close the market, see your reputation and announce a Great Fair. Once the square is built you can hide it.</t>
   </si>
   <si>
-    <t xml:space="preserve">모든 것은 시장 표식에서 시작됩니다(건설 → 기타). 광장 한가운데에 놓으세요. 반경 안에 있는 모든 노점이 이 시장에 속합니다.\n\n표식을 선택해 한 번의 클릭으로 반경을 벽에 맞추고, 노점 사용료를 설정하거나 시장을 열고 닫으며, 평판을 확인하고 대장터 개최를 공고할 수 있습니다. 광장을 완성하면 표식을 숨길 수 있습니다.</t>
+    <t xml:space="preserve">모든 것은 시장 표식에서 시작됩니다(구상 → 기타). 광장 한가운데에 놓으세요. 반경 안에 있는 모든 노점이 이 시장에 속합니다.\n\n표식을 선택해 한 번의 클릭으로 반경을 벽에 맞추고, 노점 사용료를 설정하거나 시장을 열고 닫으며, 평판을 확인하고 대장터 개최를 공고할 수 있습니다. 광장을 완성하면 표식을 숨길 수 있습니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.Guide.MarkerPlaced</t>
@@ -7730,7 +7730,7 @@
     <t xml:space="preserve">Build market stalls (Architect, Misc) inside the marker's radius. Each one needs its merchant's spot free: the cell at the end of the counter, outlined in white while you place it.\n\nCaravans walk in from the map edge and open your doors like any friendly visitor, so leave them a way in. The counter takes the colour of its material, and the awning is yours to paint from the stall.</t>
   </si>
   <si>
-    <t xml:space="preserve">시장 표식의 반경 안에 시장 노점을 지으세요(건설 → 기타). 각 노점의 상인 자리는 비워 두어야 합니다. 계산대 끝에 있는 칸으로, 배치할 때 흰색 테두리로 표시됩니다.\n\n상단은 지도 가장자리에서 걸어 들어오고 우호적인 방문객처럼 문을 열 수 있습니다. 들어올 길을 확보하세요. 계산대는 재료의 색을 따르며, 차양은 노점을 선택해 칠할 수 있습니다.</t>
+    <t xml:space="preserve">시장 표식의 반경 안에 시장 노점을 지으세요(구상 → 기타). 각 노점의 상인 자리는 비워 두어야 합니다. 계산대 끝에 있는 칸으로, 배치할 때 흰색 테두리로 표시됩니다.\n\n상단은 지도 가장자리에서 걸어 들어오고 우호적인 방문객처럼 문을 열 수 있습니다. 들어올 길을 확보하세요. 계산대는 재료의 색을 따르며, 차양은 노점을 선택해 칠할 수 있습니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.Guide.StallInside</t>
@@ -7814,7 +7814,7 @@
     <t xml:space="preserve">Two spots keep the square tidy (Architect, Misc). The caravan camp is where the pack animals wait: fence it in and they stay put. The guard rest spot is where off duty guards sit, chat and eat while one of them stands post at the stall.\n\nBoth are optional. Without them, animals and guards wait just outside the market. Each spot can be hidden once you know where it is.</t>
   </si>
   <si>
-    <t xml:space="preserve">두 지점으로 광장을 정돈할 수 있습니다(건설 → 기타). 상단 야영지는 짐꾼 동물이 기다리는 곳입니다. 울타리로 둘러싸면 동물들이 그 안에 머뭅니다. 경비원 휴식 지점은 경비원 한 명이 노점을 지키는 동안 비번인 경비원들이 앉아서 잡담하고 식사하는 곳입니다.\n\n둘 다 선택 사항입니다. 없으면 동물과 경비원이 시장 바로 밖에서 기다립니다. 각 지점의 위치를 익힌 뒤 표식을 숨길 수 있습니다.</t>
+    <t xml:space="preserve">두 지점으로 광장을 정돈할 수 있습니다(구상 → 기타). 상단 야영지는 짐꾼 동물이 기다리는 곳입니다. 울타리로 둘러싸면 동물들이 그 안에 머뭅니다. 경비원 휴식 지점은 경비원 한 명이 노점을 지키는 동안 비번인 경비원들이 앉아서 잡담하고 식사하는 곳입니다.\n\n둘 다 선택 사항입니다. 없으면 동물과 경비원이 시장 바로 밖에서 기다립니다. 각 지점의 위치를 익힌 뒤 표식을 숨길 수 있습니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.Guide.SpotCamp</t>
@@ -8012,7 +8012,7 @@
     <t xml:space="preserve">Build an auction post (Architect, Misc) inside the market. When a caravan brings slaves, the auction is announced two hours ahead and buyers come to sit in front of the post. Each lot opens at half its value.\n\nSelect the post while a lot is up to bid. If nobody outbids you, the silver comes out of your stockpiles and the slave joins your colony.</t>
   </si>
   <si>
-    <t xml:space="preserve">시장 안에 경매 기둥을 지으세요(건설 → 기타). 상단이 노예를 데려오면 두 시간 전에 경매를 공고하고, 구매자들이 기둥 앞에 앉으러 찾아옵니다. 각 노예의 시작 입찰가는 가치의 절반입니다.\n\n노예가 경매에 나와 있을 때 기둥을 선택하면 입찰할 수 있습니다. 더 높은 입찰이 없으면 보관 구역에서 은을 지불하고, 노예가 정착지에 합류합니다.</t>
+    <t xml:space="preserve">시장 안에 경매 기둥을 지으세요(구상 → 기타). 상단이 노예를 데려오면 두 시간 전에 경매를 공고하고, 구매자들이 기둥 앞에 앉으러 찾아옵니다. 각 노예의 시작 입찰가는 가치의 절반입니다.\n\n노예가 경매에 나와 있을 때 기둥을 선택하면 입찰할 수 있습니다. 더 높은 입찰이 없으면 보관 구역에서 은을 지불하고, 노예가 정착지에 합류합니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed+RimMarket.Guide.AuctionPost</t>
@@ -8886,7 +8886,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -9022,7 +9022,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>48</v>
       </c>
@@ -9073,7 +9073,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>60</v>
       </c>
@@ -9090,7 +9090,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>64</v>
       </c>
@@ -9379,7 +9379,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>132</v>
       </c>
@@ -9413,7 +9413,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>140</v>
       </c>
@@ -9447,7 +9447,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>148</v>
       </c>
@@ -9498,7 +9498,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>162</v>
       </c>
@@ -9532,7 +9532,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="195.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>170</v>
       </c>
@@ -9566,7 +9566,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="195.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>178</v>
       </c>
@@ -9600,7 +9600,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="344.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="255.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>185</v>
       </c>
@@ -9634,7 +9634,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>193</v>
       </c>
@@ -9668,7 +9668,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
         <v>202</v>
       </c>
@@ -9770,7 +9770,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
         <v>226</v>
       </c>
@@ -9804,7 +9804,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
         <v>234</v>
       </c>
@@ -9906,7 +9906,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
         <v>252</v>
       </c>
@@ -10025,7 +10025,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
         <v>282</v>
       </c>
@@ -10076,7 +10076,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
         <v>294</v>
       </c>
@@ -10246,7 +10246,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
         <v>334</v>
       </c>
@@ -10297,7 +10297,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
         <v>346</v>
       </c>
@@ -10314,7 +10314,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
         <v>350</v>
       </c>
@@ -10331,7 +10331,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
         <v>354</v>
       </c>
@@ -10399,7 +10399,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
         <v>370</v>
       </c>
@@ -10416,7 +10416,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
         <v>374</v>
       </c>
@@ -10450,7 +10450,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
         <v>382</v>
       </c>
@@ -10569,7 +10569,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
         <v>410</v>
       </c>
@@ -10671,7 +10671,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
         <v>434</v>
       </c>
@@ -10756,7 +10756,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
         <v>454</v>
       </c>
@@ -10790,7 +10790,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
         <v>462</v>
       </c>
@@ -10824,7 +10824,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
         <v>470</v>
       </c>
@@ -10960,7 +10960,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
         <v>502</v>
       </c>
@@ -10994,7 +10994,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
         <v>510</v>
       </c>
@@ -11045,7 +11045,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
         <v>522</v>
       </c>
@@ -11096,7 +11096,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
         <v>534</v>
       </c>
@@ -11130,7 +11130,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
         <v>542</v>
       </c>
@@ -11164,7 +11164,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
         <v>550</v>
       </c>
@@ -11198,7 +11198,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
         <v>558</v>
       </c>
@@ -11385,7 +11385,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
         <v>602</v>
       </c>
@@ -11419,7 +11419,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
         <v>610</v>
       </c>
@@ -11453,7 +11453,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
         <v>618</v>
       </c>
@@ -11470,7 +11470,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
         <v>622</v>
       </c>
@@ -11504,7 +11504,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
         <v>630</v>
       </c>
@@ -11623,7 +11623,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
         <v>658</v>
       </c>
@@ -11640,7 +11640,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="s">
         <v>662</v>
       </c>
@@ -11827,7 +11827,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="s">
         <v>705</v>
       </c>
@@ -11912,7 +11912,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
         <v>725</v>
       </c>
@@ -12116,7 +12116,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
         <v>773</v>
       </c>
@@ -12269,7 +12269,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
         <v>809</v>
       </c>
@@ -12405,7 +12405,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="1" t="s">
         <v>841</v>
       </c>
@@ -12439,7 +12439,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="1" t="s">
         <v>849</v>
       </c>
@@ -12507,7 +12507,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="1" t="s">
         <v>865</v>
       </c>
@@ -12524,7 +12524,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="1" t="s">
         <v>869</v>
       </c>
@@ -12592,7 +12592,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="1" t="s">
         <v>885</v>
       </c>
@@ -12660,7 +12660,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="1" t="s">
         <v>901</v>
       </c>
@@ -12711,7 +12711,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="1" t="s">
         <v>912</v>
       </c>
@@ -12745,7 +12745,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="1" t="s">
         <v>920</v>
       </c>
@@ -12762,7 +12762,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="232" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="1" t="s">
         <v>924</v>
       </c>
@@ -12796,7 +12796,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="234" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="1" t="s">
         <v>932</v>
       </c>
@@ -12932,7 +12932,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="1" t="s">
         <v>962</v>
       </c>
@@ -12949,7 +12949,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="1" t="s">
         <v>966</v>
       </c>
@@ -12966,7 +12966,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="1" t="s">
         <v>970</v>
       </c>
@@ -12983,7 +12983,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
         <v>974</v>
       </c>
@@ -13034,7 +13034,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="1" t="s">
         <v>985</v>
       </c>
@@ -13306,7 +13306,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="264" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="1" t="s">
         <v>1049</v>
       </c>
@@ -13323,7 +13323,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="265" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="1" t="s">
         <v>1053</v>
       </c>
@@ -13340,7 +13340,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="266" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="266" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="1" t="s">
         <v>1057</v>
       </c>
@@ -13391,7 +13391,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="269" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="s">
         <v>1069</v>
       </c>
@@ -13476,7 +13476,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="274" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="1" t="s">
         <v>1089</v>
       </c>
@@ -13510,7 +13510,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="276" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="276" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="1" t="s">
         <v>1097</v>
       </c>
@@ -13527,7 +13527,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="277" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="1" t="s">
         <v>1101</v>
       </c>
@@ -13544,7 +13544,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="1" t="s">
         <v>1105</v>
       </c>
@@ -13561,7 +13561,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="279" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="1" t="s">
         <v>1109</v>
       </c>
@@ -13595,7 +13595,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="281" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="1" t="s">
         <v>1117</v>
       </c>
@@ -13629,7 +13629,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="283" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="1" t="s">
         <v>1125</v>
       </c>
@@ -13646,7 +13646,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="284" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="1" t="s">
         <v>1129</v>
       </c>
@@ -13663,7 +13663,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="285" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="285" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="1" t="s">
         <v>1133</v>
       </c>
@@ -14139,7 +14139,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="313" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="1" t="s">
         <v>1243</v>
       </c>
@@ -14156,7 +14156,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="314" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="314" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="1" t="s">
         <v>1247</v>
       </c>
@@ -14173,7 +14173,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="315" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="1" t="s">
         <v>1251</v>
       </c>
@@ -14190,7 +14190,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="316" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="316" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="1" t="s">
         <v>1255</v>
       </c>
@@ -14224,7 +14224,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="318" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="318" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="1" t="s">
         <v>1263</v>
       </c>
@@ -14343,7 +14343,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="325" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="325" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="1" t="s">
         <v>1291</v>
       </c>
@@ -14394,7 +14394,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="328" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="328" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="1" t="s">
         <v>1303</v>
       </c>
@@ -14479,7 +14479,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="333" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="333" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="1" t="s">
         <v>1323</v>
       </c>
@@ -14530,7 +14530,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="336" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="336" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="1" t="s">
         <v>1335</v>
       </c>
@@ -14717,7 +14717,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="347" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="347" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="1" t="s">
         <v>1379</v>
       </c>
@@ -14802,7 +14802,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="352" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="352" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="1" t="s">
         <v>1399</v>
       </c>
@@ -14887,7 +14887,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="357" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="357" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="s">
         <v>1419</v>
       </c>
@@ -15006,7 +15006,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="364" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="364" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="1" t="s">
         <v>1447</v>
       </c>
@@ -15040,7 +15040,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="366" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="366" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="1" t="s">
         <v>1455</v>
       </c>
@@ -15108,7 +15108,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="370" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="370" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="1" t="s">
         <v>1471</v>
       </c>
@@ -15159,7 +15159,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="373" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="373" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="1" t="s">
         <v>1483</v>
       </c>
@@ -15227,7 +15227,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="377" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="377" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="1" t="s">
         <v>1499</v>
       </c>
@@ -15261,7 +15261,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="379" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="379" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="1" t="s">
         <v>1507</v>
       </c>
@@ -15329,7 +15329,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="383" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="383" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="1" t="s">
         <v>1523</v>
       </c>
@@ -15414,7 +15414,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="388" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="388" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="1" t="s">
         <v>1543</v>
       </c>
@@ -15448,7 +15448,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="390" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="390" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="1" t="s">
         <v>1551</v>
       </c>
@@ -15465,7 +15465,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="391" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="391" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="1" t="s">
         <v>1555</v>
       </c>
@@ -15550,7 +15550,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="396" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="396" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="1" t="s">
         <v>1575</v>
       </c>
@@ -15618,7 +15618,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="400" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="400" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="1" t="s">
         <v>1591</v>
       </c>
@@ -15635,7 +15635,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="401" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="401" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="s">
         <v>1595</v>
       </c>
@@ -15686,7 +15686,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="404" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="404" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="1" t="s">
         <v>1607</v>
       </c>
@@ -15737,7 +15737,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="407" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="407" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="1" t="s">
         <v>1619</v>
       </c>
@@ -15771,7 +15771,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="409" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="409" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="1" t="s">
         <v>1627</v>
       </c>
@@ -16230,7 +16230,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="436" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="436" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="1" t="s">
         <v>1735</v>
       </c>
@@ -16264,7 +16264,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="438" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="438" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="1" t="s">
         <v>1743</v>
       </c>
@@ -16298,7 +16298,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="440" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="440" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="1" t="s">
         <v>1751</v>
       </c>
@@ -16332,7 +16332,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="442" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="442" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="1" t="s">
         <v>1759</v>
       </c>
@@ -16349,7 +16349,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="443" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="443" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="1" t="s">
         <v>1763</v>
       </c>
@@ -16383,7 +16383,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="445" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="445" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="1" t="s">
         <v>1771</v>
       </c>
@@ -16400,7 +16400,7 @@
         <v>1774</v>
       </c>
     </row>
-    <row r="446" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="446" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="1" t="s">
         <v>1775</v>
       </c>
@@ -16434,7 +16434,7 @@
         <v>1782</v>
       </c>
     </row>
-    <row r="448" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="448" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="1" t="s">
         <v>1783</v>
       </c>
@@ -16468,7 +16468,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="450" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="450" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="1" t="s">
         <v>1791</v>
       </c>
@@ -16485,7 +16485,7 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="451" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="451" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="1" t="s">
         <v>1795</v>
       </c>
@@ -16536,7 +16536,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="454" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="454" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="1" t="s">
         <v>1807</v>
       </c>
@@ -16553,7 +16553,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="455" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="455" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="1" t="s">
         <v>1811</v>
       </c>
@@ -16604,7 +16604,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="458" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="458" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="1" t="s">
         <v>1823</v>
       </c>
@@ -16621,7 +16621,7 @@
         <v>1826</v>
       </c>
     </row>
-    <row r="459" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="459" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="1" t="s">
         <v>1827</v>
       </c>
@@ -16655,7 +16655,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="461" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="461" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="1" t="s">
         <v>1835</v>
       </c>
@@ -16672,7 +16672,7 @@
         <v>1838</v>
       </c>
     </row>
-    <row r="462" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="462" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="1" t="s">
         <v>1839</v>
       </c>
@@ -16706,7 +16706,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="464" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="464" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="1" t="s">
         <v>1847</v>
       </c>
@@ -16740,7 +16740,7 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="466" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="466" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="1" t="s">
         <v>1855</v>
       </c>
@@ -16774,7 +16774,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="468" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="468" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="1" t="s">
         <v>1863</v>
       </c>
@@ -16808,7 +16808,7 @@
         <v>1870</v>
       </c>
     </row>
-    <row r="470" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="470" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="1" t="s">
         <v>1871</v>
       </c>
@@ -16910,7 +16910,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="476" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="476" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="1" t="s">
         <v>1895</v>
       </c>
@@ -16978,7 +16978,7 @@
         <v>1910</v>
       </c>
     </row>
-    <row r="480" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="480" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="1" t="s">
         <v>1911</v>
       </c>
@@ -17046,7 +17046,7 @@
         <v>1925</v>
       </c>
     </row>
-    <row r="484" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="484" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="1" t="s">
         <v>1926</v>
       </c>
@@ -17063,7 +17063,7 @@
         <v>1929</v>
       </c>
     </row>
-    <row r="485" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="485" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="1" t="s">
         <v>1930</v>
       </c>
@@ -17250,7 +17250,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="496" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="496" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="1" t="s">
         <v>1974</v>
       </c>
@@ -17267,7 +17267,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="497" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="497" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="1" t="s">
         <v>1978</v>
       </c>
@@ -17284,7 +17284,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="498" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="498" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="1" t="s">
         <v>1982</v>
       </c>
@@ -17318,7 +17318,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="500" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="500" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="1" t="s">
         <v>1990</v>
       </c>
@@ -17335,7 +17335,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="501" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="501" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="1" t="s">
         <v>1994</v>
       </c>
@@ -17420,7 +17420,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="506" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="506" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="1" t="s">
         <v>2014</v>
       </c>
@@ -17539,7 +17539,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="513" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="513" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="1" t="s">
         <v>2042</v>
       </c>
@@ -17590,7 +17590,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="516" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="516" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="1" t="s">
         <v>2054</v>
       </c>
@@ -17760,7 +17760,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="526" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="526" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="1" t="s">
         <v>2094</v>
       </c>
@@ -17913,7 +17913,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="535" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="535" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="1" t="s">
         <v>2128</v>
       </c>
@@ -17964,7 +17964,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="538" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="538" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="1" t="s">
         <v>2140</v>
       </c>
@@ -18015,7 +18015,7 @@
         <v>2151</v>
       </c>
     </row>
-    <row r="541" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="541" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="1" t="s">
         <v>2152</v>
       </c>
@@ -18032,7 +18032,7 @@
         <v>2155</v>
       </c>
     </row>
-    <row r="542" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="542" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="1" t="s">
         <v>2156</v>
       </c>
@@ -18066,7 +18066,7 @@
         <v>2163</v>
       </c>
     </row>
-    <row r="544" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="544" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A544" s="1" t="s">
         <v>2164</v>
       </c>
@@ -18100,7 +18100,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="546" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="546" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="1" t="s">
         <v>2172</v>
       </c>
@@ -18134,7 +18134,7 @@
         <v>2179</v>
       </c>
     </row>
-    <row r="548" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="548" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A548" s="1" t="s">
         <v>2180</v>
       </c>
@@ -18168,7 +18168,7 @@
         <v>2187</v>
       </c>
     </row>
-    <row r="550" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="550" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A550" s="1" t="s">
         <v>2188</v>
       </c>
@@ -18202,7 +18202,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="552" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="552" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A552" s="1" t="s">
         <v>2196</v>
       </c>
@@ -18253,7 +18253,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="555" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="555" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="1" t="s">
         <v>2208</v>
       </c>
@@ -18270,7 +18270,7 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="556" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="556" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="1" t="s">
         <v>2212</v>
       </c>
@@ -18355,7 +18355,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="561" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="561" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A561" s="1" t="s">
         <v>2232</v>
       </c>
@@ -18474,7 +18474,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="568" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="568" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A568" s="1" t="s">
         <v>2260</v>
       </c>
@@ -18508,7 +18508,7 @@
         <v>2267</v>
       </c>
     </row>
-    <row r="570" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="570" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A570" s="1" t="s">
         <v>2268</v>
       </c>
@@ -18576,7 +18576,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="574" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="574" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A574" s="1" t="s">
         <v>2284</v>
       </c>
@@ -18678,7 +18678,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="580" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="580" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A580" s="1" t="s">
         <v>2308</v>
       </c>
@@ -18712,7 +18712,7 @@
         <v>2315</v>
       </c>
     </row>
-    <row r="582" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="582" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A582" s="1" t="s">
         <v>2316</v>
       </c>
@@ -18746,7 +18746,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="584" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="584" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A584" s="1" t="s">
         <v>2324</v>
       </c>
@@ -18882,7 +18882,7 @@
         <v>2355</v>
       </c>
     </row>
-    <row r="592" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="592" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A592" s="1" t="s">
         <v>2356</v>
       </c>
@@ -18899,7 +18899,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="593" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="593" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A593" s="1" t="s">
         <v>2360</v>
       </c>
@@ -18916,7 +18916,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="594" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="594" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A594" s="1" t="s">
         <v>2364</v>
       </c>
@@ -18933,7 +18933,7 @@
         <v>2367</v>
       </c>
     </row>
-    <row r="595" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="595" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A595" s="1" t="s">
         <v>2368</v>
       </c>
@@ -18950,7 +18950,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="596" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="596" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A596" s="1" t="s">
         <v>2372</v>
       </c>
@@ -19001,7 +19001,7 @@
         <v>2383</v>
       </c>
     </row>
-    <row r="599" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="599" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A599" s="1" t="s">
         <v>2384</v>
       </c>
@@ -19052,7 +19052,7 @@
         <v>2395</v>
       </c>
     </row>
-    <row r="602" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="602" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A602" s="1" t="s">
         <v>2396</v>
       </c>
@@ -19120,7 +19120,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="606" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="606" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A606" s="1" t="s">
         <v>2412</v>
       </c>
@@ -19137,7 +19137,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="607" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="607" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A607" s="1" t="s">
         <v>2416</v>
       </c>
@@ -19171,7 +19171,7 @@
         <v>2423</v>
       </c>
     </row>
-    <row r="609" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="609" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A609" s="1" t="s">
         <v>2424</v>
       </c>
@@ -19188,7 +19188,7 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="610" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="610" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A610" s="1" t="s">
         <v>2428</v>
       </c>
@@ -19205,7 +19205,7 @@
         <v>2431</v>
       </c>
     </row>
-    <row r="611" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="611" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A611" s="1" t="s">
         <v>2432</v>
       </c>
@@ -19392,7 +19392,7 @@
         <v>2475</v>
       </c>
     </row>
-    <row r="622" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="622" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A622" s="1" t="s">
         <v>2476</v>
       </c>
@@ -19426,7 +19426,7 @@
         <v>2483</v>
       </c>
     </row>
-    <row r="624" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="624" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A624" s="1" t="s">
         <v>2484</v>
       </c>
@@ -19477,7 +19477,7 @@
         <v>2494</v>
       </c>
     </row>
-    <row r="627" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="627" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A627" s="1" t="s">
         <v>2495</v>
       </c>
@@ -19715,7 +19715,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="641" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="641" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A641" s="1" t="s">
         <v>2550</v>
       </c>
@@ -19783,7 +19783,7 @@
         <v>2564</v>
       </c>
     </row>
-    <row r="645" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="645" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A645" s="1" t="s">
         <v>2565</v>
       </c>
@@ -19851,7 +19851,7 @@
         <v>2580</v>
       </c>
     </row>
-    <row r="649" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="649" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A649" s="1" t="s">
         <v>2581</v>
       </c>
@@ -19902,7 +19902,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="652" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="652" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A652" s="1" t="s">
         <v>2593</v>
       </c>
@@ -19970,7 +19970,7 @@
         <v>2608</v>
       </c>
     </row>
-    <row r="656" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="656" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A656" s="1" t="s">
         <v>2609</v>
       </c>
@@ -20055,7 +20055,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="661" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="661" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A661" s="1" t="s">
         <v>2626</v>
       </c>
@@ -20123,7 +20123,7 @@
         <v>2641</v>
       </c>
     </row>
-    <row r="665" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="665" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A665" s="1" t="s">
         <v>2642</v>
       </c>
@@ -20174,7 +20174,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="668" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="668" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A668" s="1" t="s">
         <v>2653</v>
       </c>
@@ -20208,7 +20208,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="670" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="670" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A670" s="1" t="s">
         <v>2659</v>
       </c>
@@ -20259,7 +20259,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="673" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="673" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A673" s="1" t="s">
         <v>2671</v>
       </c>
@@ -20293,7 +20293,7 @@
         <v>2678</v>
       </c>
     </row>
-    <row r="675" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="675" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A675" s="1" t="s">
         <v>2679</v>
       </c>
@@ -20344,7 +20344,7 @@
         <v>2688</v>
       </c>
     </row>
-    <row r="678" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="678" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A678" s="1" t="s">
         <v>2689</v>
       </c>
@@ -20361,7 +20361,7 @@
         <v>2692</v>
       </c>
     </row>
-    <row r="679" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="679" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A679" s="1" t="s">
         <v>2693</v>
       </c>
@@ -20480,7 +20480,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="686" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="686" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A686" s="1" t="s">
         <v>2721</v>
       </c>
@@ -20939,7 +20939,7 @@
         <v>2819</v>
       </c>
     </row>
-    <row r="713" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="713" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A713" s="1" t="s">
         <v>2820</v>
       </c>
@@ -20956,7 +20956,7 @@
         <v>2823</v>
       </c>
     </row>
-    <row r="714" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="714" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A714" s="1" t="s">
         <v>2824</v>
       </c>
@@ -20990,7 +20990,7 @@
         <v>2831</v>
       </c>
     </row>
-    <row r="716" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="716" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A716" s="1" t="s">
         <v>2832</v>
       </c>
